--- a/docs/equipment_db.xlsx
+++ b/docs/equipment_db.xlsx
@@ -49,7 +49,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">tools/equip_balance.cjs --calibrate (</t>
+          <t xml:space="preserve">tools/equip_balance.cjs --calibrate → --calib-merge (</t>
         </r>
         <r>
           <rPr>
@@ -65,7 +65,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </r>
         <r>
           <rPr>
@@ -105,23 +105,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">적 배율을 이분 탐색해 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">4</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">스테이지 일반</t>
+          <t xml:space="preserve">적 배율을 로그 이분 탐색해 일반</t>
         </r>
         <r>
           <rPr>
@@ -153,7 +137,23 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">보스 평균 승률이 </t>
+          <t xml:space="preserve">보스 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">종 승률이 </t>
         </r>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">. </t>
+          <t xml:space="preserve">. C</t>
         </r>
         <r>
           <rPr>
@@ -185,7 +185,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">시드 수가 적어 잡음이 있어 </t>
+          <t xml:space="preserve">열 </t>
         </r>
         <r>
           <rPr>
@@ -193,7 +193,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">= </t>
         </r>
         <r>
           <rPr>
@@ -201,7 +201,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">열 회귀 곡선을 채택</t>
+          <t xml:space="preserve">이 값 </t>
         </r>
         <r>
           <rPr>
@@ -209,7 +209,39 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">÷ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">장비 없음 값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(0.905). </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">잡음 약 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">±10%.</t>
         </r>
       </text>
     </comment>
@@ -320,7 +352,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="608">
   <si>
     <r>
       <rPr>
@@ -9559,7 +9591,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">권장 등급 풀세트로 기믹 공략 시 승률 </t>
+      <t xml:space="preserve">권장 등급 풀세트 </t>
     </r>
     <r>
       <rPr>
@@ -9570,7 +9602,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">85%</t>
+      <t xml:space="preserve">+5</t>
     </r>
     <r>
       <rPr>
@@ -9580,7 +9612,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 되는 지점 </t>
+      <t xml:space="preserve">강</t>
     </r>
     <r>
       <rPr>
@@ -9601,7 +9633,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시뮬 보정 → 로그 회귀</t>
+      <t xml:space="preserve">레벨 차 </t>
     </r>
     <r>
       <rPr>
@@ -9612,96 +9644,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">단계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 체력 배율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 공격력 배율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">권장 장비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보정 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(85% </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회귀 곡선</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전 단계 대비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">견습</t>
-  </si>
-  <si>
-    <t xml:space="preserve">숙련</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정예</t>
-  </si>
-  <si>
-    <t xml:space="preserve">영웅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전설</t>
-  </si>
-  <si>
-    <t xml:space="preserve">신화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">태초</t>
-  </si>
-  <si>
+      <t xml:space="preserve">0)</t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -9710,7 +9654,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">배율 </t>
+      <t xml:space="preserve">으로 탱커 파티 승률 </t>
     </r>
     <r>
       <rPr>
@@ -9721,7 +9665,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.00 = </t>
+      <t xml:space="preserve">85% </t>
     </r>
     <r>
       <rPr>
@@ -9731,7 +9675,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">데모 기본 던전</t>
+      <t xml:space="preserve">지점 </t>
     </r>
     <r>
       <rPr>
@@ -9742,7 +9686,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">÷ </t>
     </r>
     <r>
       <rPr>
@@ -9752,7 +9696,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장비 없음</t>
+      <t xml:space="preserve">장비 없음 기준 </t>
     </r>
     <r>
       <rPr>
@@ -9763,7 +9707,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -9773,7 +9717,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">견습</t>
+      <t xml:space="preserve">짓누름</t>
     </r>
     <r>
       <rPr>
@@ -9784,7 +9728,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(T1)</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -9794,7 +9738,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부터 장비를 갖춘 원정대를 가정</t>
+      <t xml:space="preserve">레벨 보정 반영</t>
     </r>
     <r>
       <rPr>
@@ -9805,23 +9749,48 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">단계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 체력 배율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 공격력 배율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">권장 장비</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">드랍 테이블 </t>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85% </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="14"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -9831,22 +9800,54 @@
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급 확률</t>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절대</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="14"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">던전 레벨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전 단계 대비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">견습</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숙련</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정예</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영웅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전설</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">태초</t>
   </si>
   <si>
     <r>
@@ -9857,7 +9858,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가중치</t>
+      <t xml:space="preserve">배율 </t>
     </r>
     <r>
       <rPr>
@@ -9868,7 +9869,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">1.00 = </t>
     </r>
     <r>
       <rPr>
@@ -9878,7 +9879,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">입력</t>
+      <t xml:space="preserve">데모 기본 던전</t>
     </r>
     <r>
       <rPr>
@@ -9889,7 +9890,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) → </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -9899,7 +9900,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확률</t>
+      <t xml:space="preserve">장비 없음</t>
     </r>
     <r>
       <rPr>
@@ -9910,7 +9911,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">). </t>
     </r>
     <r>
       <rPr>
@@ -9920,7 +9921,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수식</t>
+      <t xml:space="preserve">견습</t>
     </r>
     <r>
       <rPr>
@@ -9931,7 +9932,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">(T1)</t>
     </r>
     <r>
       <rPr>
@@ -9941,7 +9942,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">출처별 중심 등급</t>
+      <t xml:space="preserve">부터 장비를 갖춘 원정대를 가정</t>
     </r>
     <r>
       <rPr>
@@ -9952,8 +9953,50 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">드랍 테이블 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 확률</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -9962,7 +10005,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일반 </t>
+      <t xml:space="preserve">가중치</t>
     </r>
     <r>
       <rPr>
@@ -9973,7 +10016,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-0.6, </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -9983,7 +10026,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정예 </t>
+      <t xml:space="preserve">입력</t>
     </r>
     <r>
       <rPr>
@@ -9994,7 +10037,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.4, </t>
+      <t xml:space="preserve">) → </t>
     </r>
     <r>
       <rPr>
@@ -10004,7 +10047,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보스 </t>
+      <t xml:space="preserve">확률</t>
     </r>
     <r>
       <rPr>
@@ -10015,7 +10058,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+1.0, </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -10025,7 +10068,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">상점 </t>
+      <t xml:space="preserve">수식</t>
     </r>
     <r>
       <rPr>
@@ -10036,7 +10079,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-1.0 (</t>
+      <t xml:space="preserve">). </t>
     </r>
     <r>
       <rPr>
@@ -10046,7 +10089,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">난이도 단계 기준</t>
+      <t xml:space="preserve">출처별 중심 등급</t>
     </r>
     <r>
       <rPr>
@@ -10057,532 +10100,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일반 전투 보상</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">택</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중 장비 카드</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">난이도</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SSR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가중치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SSR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정예 처치</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보스 처치</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장비 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 + </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보석 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">던전 상인 판매</t>
-  </si>
-  <si>
-    <t xml:space="preserve">갑옷 랜덤 패시브</t>
-  </si>
-  <si>
+      <t xml:space="preserve">: </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -10591,7 +10110,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이름 고정</t>
+      <t xml:space="preserve">일반 </t>
     </r>
     <r>
       <rPr>
@@ -10602,7 +10121,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">-0.6, </t>
     </r>
     <r>
       <rPr>
@@ -10612,7 +10131,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">등급 </t>
+      <t xml:space="preserve">정예 </t>
     </r>
     <r>
       <rPr>
@@ -10623,7 +10142,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">+0.4, </t>
     </r>
     <r>
       <rPr>
@@ -10633,7 +10152,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">배율</t>
+      <t xml:space="preserve">보스 </t>
     </r>
     <r>
       <rPr>
@@ -10644,7 +10163,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">+1.0, </t>
     </r>
     <r>
       <rPr>
@@ -10654,7 +10173,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">패시브 등급은 장비 등급 이하에서 굴림 </t>
+      <t xml:space="preserve">상점 </t>
     </r>
     <r>
       <rPr>
@@ -10665,7 +10184,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">-1.0 (</t>
     </r>
     <r>
       <rPr>
@@ -10675,7 +10194,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">같음</t>
+      <t xml:space="preserve">난이도 단계 기준</t>
     </r>
     <r>
       <rPr>
@@ -10686,8 +10205,532 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/−1/−2/</t>
-    </r>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반 전투 보상</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">택</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 장비 카드</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">난이도</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SSR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가중치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SSR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정예 처치</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보스 처치</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장비 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보석 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">던전 상인 판매</t>
+  </si>
+  <si>
+    <t xml:space="preserve">갑옷 랜덤 패시브</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -10696,7 +10739,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">그 아래 </t>
+      <t xml:space="preserve">이름 고정</t>
     </r>
     <r>
       <rPr>
@@ -10707,7 +10750,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -10717,7 +10760,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가중치</t>
+      <t xml:space="preserve">등급 </t>
     </r>
     <r>
       <rPr>
@@ -10728,7 +10771,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -10738,7 +10781,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">같은 이름은 최고 등급 하나만 적용</t>
+      <t xml:space="preserve">배율</t>
     </r>
     <r>
       <rPr>
@@ -10749,744 +10792,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">등급 굴림 가중치</t>
-  </si>
-  <si>
-    <t xml:space="preserve">같은 등급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">−3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이하</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">등급 배율 →</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최저 등급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">종류</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준 값</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">고정 단점</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron_heart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">무쇠 심장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수치형</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP +[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">trained_arm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단련된 팔</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공격력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">light_feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가벼운 발</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이동 속도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">clear_mind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">맑은 정신</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">oath_guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수호의 맹세</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받는 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">breaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부수는 손</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그로기 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">hawk_eye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">매의 눈</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">치명타 확률 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">finisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결정타</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그로기 적에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">firefly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">반딧불 신호</t>
-  </si>
-  <si>
-    <t xml:space="preserve">규칙형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first_breath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">첫 숨결</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전투 시작 시 필살기 게이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">stubborn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">끈질긴 생명</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 25% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이하가 되면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무적 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전투당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter_rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">여우비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적이 그로기에 빠지면 ② 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">감소</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">old_root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">늙은 참나무의 뿌리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트레이드오프</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이동 속도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">berserk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광전사의 피</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받는 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+12%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">moon_oath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">달빛 맹세</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그로기 게이지가 있는 적이 그로기가 아닐 때 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">first_light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">숲의 첫 숨</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필살기 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">필살기 게이지는 그로기 적이 있을 때만 참</t>
-  </si>
-  <si>
-    <t xml:space="preserve">장비 강화</t>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -11495,7 +10802,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실패 보정</t>
+      <t xml:space="preserve">패시브 등급은 장비 등급 이하에서 굴림 </t>
     </r>
     <r>
       <rPr>
@@ -11506,7 +10813,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -11516,7 +10823,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실패마다 기본 확률의 </t>
+      <t xml:space="preserve">같음</t>
     </r>
     <r>
       <rPr>
@@ -11527,7 +10834,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10%</t>
+      <t xml:space="preserve">/−1/−2/</t>
     </r>
     <r>
       <rPr>
@@ -11537,7 +10844,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">씩</t>
+      <t xml:space="preserve">그 아래 </t>
     </r>
     <r>
       <rPr>
@@ -11548,7 +10855,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -11558,7 +10865,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">최대 </t>
+      <t xml:space="preserve">가중치</t>
     </r>
     <r>
       <rPr>
@@ -11569,7 +10876,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">). </t>
     </r>
     <r>
       <rPr>
@@ -11579,7 +10886,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">배</t>
+      <t xml:space="preserve">같은 이름은 최고 등급 하나만 적용</t>
     </r>
     <r>
       <rPr>
@@ -11590,8 +10897,744 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">등급 굴림 가중치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">−3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이하</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">등급 배율 →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최저 등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종류</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준 값</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">고정 단점</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron_heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무쇠 심장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수치형</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP +[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">trained_arm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단련된 팔</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공격력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">light_feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가벼운 발</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이동 속도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">clear_mind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맑은 정신</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쿨타임 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">oath_guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수호의 맹세</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받는 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부수는 손</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그로기 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">hawk_eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">매의 눈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">치명타 확률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">finisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결정타</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그로기 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">firefly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">반딧불 신호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">규칙형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first_breath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">첫 숨결</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투 시작 시 필살기 게이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">stubborn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">끈질긴 생명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 25% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이하가 되면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter_rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">여우비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적이 그로기에 빠지면 ② 쿨타임 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감소</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">old_root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늙은 참나무의 뿌리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트레이드오프</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이동 속도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">berserk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광전사의 피</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받는 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">moon_oath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 맹세</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그로기 게이지가 있는 적이 그로기가 아닐 때 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">first_light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숲의 첫 숨</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필살기 위력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">필살기 게이지는 그로기 적이 있을 때만 참</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장비 강화</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -11600,7 +11643,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장인의 기운 </t>
+      <t xml:space="preserve">실패 보정</t>
     </r>
     <r>
       <rPr>
@@ -11611,7 +11654,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+= </t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -11621,7 +11664,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">현재 확률 </t>
+      <t xml:space="preserve">실패마다 기본 확률의 </t>
     </r>
     <r>
       <rPr>
@@ -11632,7 +11675,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">× 0.465, 100%</t>
+      <t xml:space="preserve">10%</t>
     </r>
     <r>
       <rPr>
@@ -11642,7 +11685,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">면 확정 성공</t>
+      <t xml:space="preserve">씩</t>
     </r>
     <r>
       <rPr>
@@ -11653,7 +11696,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -11663,7 +11706,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장비 파괴</t>
+      <t xml:space="preserve">최대 </t>
     </r>
     <r>
       <rPr>
@@ -11674,7 +11717,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -11684,7 +11727,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">단계 하락 없음</t>
+      <t xml:space="preserve">배</t>
     </r>
     <r>
       <rPr>
@@ -11695,257 +11738,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">단계당 주 스탯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보정 단위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">장인 계수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">목표 단계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 확률</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대 확률</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보정</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">강화석</t>
-  </si>
-  <si>
-    <t xml:space="preserve">골드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주 스탯 누적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기운만으로 확정까지 실패 횟수</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">근사</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">외형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외형 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">+6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외형 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">+11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외형 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">등급별 강화 한도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">분해 시 강화석</t>
-  </si>
-  <si>
+      <t xml:space="preserve">). </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -11954,7 +11748,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">분해 강화석 </t>
+      <t xml:space="preserve">장인의 기운 </t>
     </r>
     <r>
       <rPr>
@@ -11965,7 +11759,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">+= </t>
     </r>
     <r>
       <rPr>
@@ -11975,7 +11769,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">등급 값 </t>
+      <t xml:space="preserve">현재 확률 </t>
     </r>
     <r>
       <rPr>
@@ -11986,7 +11780,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+ </t>
+      <t xml:space="preserve">× 0.465, 100%</t>
     </r>
     <r>
       <rPr>
@@ -11996,7 +11790,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">강화 단계</t>
+      <t xml:space="preserve">면 확정 성공</t>
     </r>
     <r>
       <rPr>
@@ -12017,7 +11811,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전투 보상 강화석</t>
+      <t xml:space="preserve">장비 파괴</t>
     </r>
     <r>
       <rPr>
@@ -12028,7 +11822,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -12038,7 +11832,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일반 </t>
+      <t xml:space="preserve">단계 하락 없음</t>
     </r>
     <r>
       <rPr>
@@ -12049,8 +11843,257 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 · </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">단계당 주 스탯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보정 단위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장인 계수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">목표 단계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 확률</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대 확률</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보정</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">강화석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">골드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주 스탯 누적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기운만으로 확정까지 실패 횟수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근사</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">외형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">+11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">등급별 강화 한도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">분해 시 강화석</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -12059,7 +12102,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정예 </t>
+      <t xml:space="preserve">분해 강화석 </t>
     </r>
     <r>
       <rPr>
@@ -12070,7 +12113,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4 · </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -12080,7 +12123,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보스 </t>
+      <t xml:space="preserve">등급 값 </t>
     </r>
     <r>
       <rPr>
@@ -12091,13 +12134,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">밸런스 분석</t>
-  </si>
-  <si>
+      <t xml:space="preserve">+ </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -12106,7 +12144,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전투력</t>
+      <t xml:space="preserve">강화 단계</t>
     </r>
     <r>
       <rPr>
@@ -12117,7 +12155,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(%) = </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -12127,7 +12165,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장비 풀세트</t>
+      <t xml:space="preserve">전투 보상 강화석</t>
     </r>
     <r>
       <rPr>
@@ -12138,7 +12176,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(6</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -12148,7 +12186,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부위</t>
+      <t xml:space="preserve">일반 </t>
     </r>
     <r>
       <rPr>
@@ -12159,7 +12197,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">2 · </t>
     </r>
     <r>
       <rPr>
@@ -12169,7 +12207,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 올려주는 전투력 근사</t>
+      <t xml:space="preserve">정예 </t>
     </r>
     <r>
       <rPr>
@@ -12180,7 +12218,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">4 · </t>
     </r>
     <r>
       <rPr>
@@ -12190,7 +12228,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">승률 </t>
+      <t xml:space="preserve">보스 </t>
     </r>
     <r>
       <rPr>
@@ -12201,8 +12239,13 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
+      <t xml:space="preserve">8.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">밸런스 분석</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -12211,7 +12254,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">헤드리스 전투 시뮬</t>
+      <t xml:space="preserve">전투력</t>
     </r>
     <r>
       <rPr>
@@ -12222,68 +12265,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 등급별 풀세트 전투력</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(%) — </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직업별 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기대값</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">E/UR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">평균</t>
-  </si>
-  <si>
-    <t xml:space="preserve">직업 편차</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(%) = </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -12292,7 +12275,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직업 간 편차가 작을수록 공정</t>
+      <t xml:space="preserve">장비 풀세트</t>
     </r>
     <r>
       <rPr>
@@ -12303,7 +12286,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">(6</t>
     </r>
     <r>
       <rPr>
@@ -12313,7 +12296,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">목표 </t>
+      <t xml:space="preserve">부위</t>
     </r>
     <r>
       <rPr>
@@ -12324,7 +12307,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">±5% </t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -12334,7 +12317,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이내</t>
+      <t xml:space="preserve">가 올려주는 전투력 근사</t>
     </r>
     <r>
       <rPr>
@@ -12345,630 +12328,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 전투력 구성 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탱커 기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, %)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">구성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주 스탯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추가 옵션</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 최대 누적 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상한 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(E </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">풀세트 최악의 경우</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">최대 누적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상한 초과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출처</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옵션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) + E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보석 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 스탯 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">특성 스탯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메달</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옵션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) + E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보석 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 스탯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옵션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 스탯</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">상한 없음</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옵션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부위당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 스탯 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">특성 스탯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메달</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -12977,7 +12338,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">초과분은 게임에서 상한으로 잘림 </t>
+      <t xml:space="preserve">승률 </t>
     </r>
     <r>
       <rPr>
@@ -12988,7 +12349,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(CONST.STAT_CAPS). </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -12998,7 +12359,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일부러 한 스탯을 몰아도 상한까지만 → 빌드 다양성 유도</t>
+      <t xml:space="preserve">헤드리스 전투 시뮬</t>
     </r>
     <r>
       <rPr>
@@ -13020,7 +12381,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">④ 시뮬 승률 — 기믹 공략 </t>
+      <t xml:space="preserve">① 등급별 풀세트 전투력</t>
     </r>
     <r>
       <rPr>
@@ -13030,7 +12391,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">(%) — </t>
     </r>
     <r>
       <rPr>
@@ -13039,7 +12400,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기절로 차지 끊기</t>
+      <t xml:space="preserve">직업별 </t>
     </r>
     <r>
       <rPr>
@@ -13049,7 +12410,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
@@ -13058,37 +12419,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">그로기에 필살기 집중</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험 범위 회피</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+      <t xml:space="preserve">기대값</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">E/UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">평균</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 편차</t>
   </si>
   <si>
     <r>
@@ -13099,7 +12440,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">행 </t>
+      <t xml:space="preserve">직업 간 편차가 작을수록 공정</t>
     </r>
     <r>
       <rPr>
@@ -13110,7 +12451,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -13120,7 +12461,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">난이도</t>
+      <t xml:space="preserve">목표 </t>
     </r>
     <r>
       <rPr>
@@ -13131,7 +12472,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">±5% </t>
     </r>
     <r>
       <rPr>
@@ -13141,7 +12482,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">열 </t>
+      <t xml:space="preserve">이내</t>
     </r>
     <r>
       <rPr>
@@ -13152,8 +12493,630 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">② 전투력 구성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탱커 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, %)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">구성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주 스탯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추가 옵션</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 최대 누적 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상한 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(E </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀세트 최악의 경우</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">최대 누적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상한 초과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출처</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보석 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 스탯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">특성 스탯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보석 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 스탯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 스탯</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">상한 없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 스탯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">특성 스탯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -13162,7 +13125,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장비 등급</t>
+      <t xml:space="preserve">초과분은 게임에서 상한으로 잘림 </t>
     </r>
     <r>
       <rPr>
@@ -13173,7 +13136,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">(CONST.STAT_CAPS). </t>
     </r>
     <r>
       <rPr>
@@ -13183,7 +13146,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">값 </t>
+      <t xml:space="preserve">일부러 한 스탯을 몰아도 상한까지만 → 빌드 다양성 유도</t>
     </r>
     <r>
       <rPr>
@@ -13194,8 +13157,145 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">④ 단계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장비 등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탱커 유무 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기믹 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시드 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, +5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -13204,7 +13304,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일반</t>
+      <t xml:space="preserve">값 </t>
     </r>
     <r>
       <rPr>
@@ -13215,7 +13315,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">= (</t>
     </r>
     <r>
       <rPr>
@@ -13225,7 +13325,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정예</t>
+      <t xml:space="preserve">일반 </t>
     </r>
     <r>
       <rPr>
@@ -13236,7 +13336,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">+ </t>
     </r>
     <r>
       <rPr>
@@ -13246,7 +13346,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보스 평균 승률</t>
+      <t xml:space="preserve">정예 </t>
     </r>
     <r>
       <rPr>
@@ -13257,7 +13357,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">+ </t>
     </r>
     <r>
       <rPr>
@@ -13267,7 +13367,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">대각선</t>
+      <t xml:space="preserve">보스</t>
     </r>
     <r>
       <rPr>
@@ -13278,7 +13378,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">×2) / 4 </t>
     </r>
     <r>
       <rPr>
@@ -13288,7 +13388,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">권장 등급</t>
+      <t xml:space="preserve">승률</t>
     </r>
     <r>
       <rPr>
@@ -13299,7 +13399,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -13309,7 +13409,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이 기믹 기준 </t>
+      <t xml:space="preserve">탱커 </t>
     </r>
     <r>
       <rPr>
@@ -13320,7 +13420,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">85% </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -13330,7 +13430,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">근처가 목표</t>
+      <t xml:space="preserve">토비</t>
     </r>
     <r>
       <rPr>
@@ -13341,485 +13441,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견습 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(UC)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">숙련 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(C)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정예 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(R)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영웅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(SR)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전설 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(SSR)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신화 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(UR)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(L)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태초 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(E)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">⑤ 시뮬 승률 — 딜만 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쿨마다 스킬 난사</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가까운 적만 공격</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">⑥ 딜찍누 지수 — 같은 등급에서 기믹 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">딜만</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">딜만으로 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">85%</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">를 넘으려면 필요한 등급 차이</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">권장 등급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기믹 승률</t>
-  </si>
-  <si>
-    <t xml:space="preserve">딜만 승률</t>
-  </si>
-  <si>
-    <t xml:space="preserve">차이</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">딜만 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">85%</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 필요한 추가 등급</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장비 범위 안에서 불가</t>
-  </si>
-  <si>
+      <t xml:space="preserve">+</t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -13828,7 +13451,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시뮬 결과 값은 </t>
+      <t xml:space="preserve">단비</t>
     </r>
     <r>
       <rPr>
@@ -13839,7 +13462,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tools/equip_balance.cjs (SEEDS=4, </t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -13849,7 +13472,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">조합 </t>
+      <t xml:space="preserve">보리 </t>
     </r>
     <r>
       <rPr>
@@ -13860,7 +13483,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -13870,7 +13493,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개</t>
+      <t xml:space="preserve">토비</t>
     </r>
     <r>
       <rPr>
@@ -13881,7 +13504,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -13891,7 +13514,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실행 결과</t>
+      <t xml:space="preserve">별비</t>
     </r>
     <r>
       <rPr>
@@ -13902,7 +13525,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -13912,7 +13535,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">재생성</t>
+      <t xml:space="preserve">솔담</t>
     </r>
     <r>
       <rPr>
@@ -13923,7 +13546,384 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: node tools/equip_balance.cjs → python3 tools/build_equipment_xlsx.py</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탱커 없음 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단비</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">별비</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보리 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">별비</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">솔담</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보리</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">괄호 열 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레벨 차</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">적 배율</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨 차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">탱커 없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T1 (UC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2 (C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3 (R)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4 (SR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T5 (SSR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6 (UR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7 (L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8 (E)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재생성</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: SEEDS=8 node tools/equip_balance.cjs --nosim --tier-matrix → python3 tools/build_equipment_xlsx.py</t>
     </r>
   </si>
 </sst>
@@ -13931,7 +13931,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -13940,7 +13940,6 @@
     <numFmt numFmtId="169" formatCode="0.00%"/>
     <numFmt numFmtId="170" formatCode="General"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
-    <numFmt numFmtId="172" formatCode="\+0%;\-0%;0%"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -14152,7 +14151,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -14310,10 +14309,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14866,7 +14861,7 @@
       <c r="E4" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="15" t="s">
         <v>429</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -14884,20 +14879,20 @@
         <v>432</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">C5</f>
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>43</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>1.39</v>
+        <v>1.137</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>78</v>
@@ -14911,24 +14906,24 @@
         <v>433</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="D6" s="25" t="n">
         <f aca="false">C6</f>
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>1.549</v>
+        <v>1.289</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="H6" s="11" t="n">
         <f aca="false">C6/C5-1</f>
-        <v>0.0596026490066226</v>
+        <v>0.126984126984127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14939,24 +14934,24 @@
         <v>434</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="D7" s="25" t="n">
         <f aca="false">C7</f>
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>1.743</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>1.805</v>
+        <v>1.512</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">C7/C6-1</f>
-        <v>0.0874999999999999</v>
+        <v>0.176056338028169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14967,11 +14962,11 @@
         <v>435</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="D8" s="25" t="n">
         <f aca="false">C8</f>
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>46</v>
@@ -14979,12 +14974,12 @@
       <c r="F8" s="31" t="n">
         <v>2.067</v>
       </c>
-      <c r="G8" s="31" t="n">
-        <v>2.193</v>
+      <c r="G8" s="10" t="n">
+        <v>45</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">C8/C7-1</f>
-        <v>0.189655172413793</v>
+        <v>0.365269461077844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14995,24 +14990,24 @@
         <v>436</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="D9" s="25" t="n">
         <f aca="false">C9</f>
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <v>2.691</v>
+        <v>2.31</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">C9/C8-1</f>
-        <v>0.217391304347826</v>
+        <v>0.118421052631579</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15023,24 +15018,24 @@
         <v>437</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">C10</f>
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>3.091</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>3.363</v>
+        <v>2.966</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">C10/C9-1</f>
-        <v>0.226190476190476</v>
+        <v>0.286274509803922</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15051,24 +15046,24 @@
         <v>438</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="D11" s="25" t="n">
         <f aca="false">C11</f>
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>4.187</v>
-      </c>
-      <c r="G11" s="31" t="n">
-        <v>4.021</v>
+        <v>3.861</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">C11/C10-1</f>
-        <v>0.355987055016181</v>
+        <v>0.301829268292683</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15079,24 +15074,24 @@
         <v>439</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>5.1</v>
+        <v>5.83</v>
       </c>
       <c r="D12" s="25" t="n">
         <f aca="false">C12</f>
-        <v>5.1</v>
+        <v>5.83</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>51</v>
       </c>
       <c r="F12" s="31" t="n">
-        <v>5.104</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>4.666</v>
+        <v>5.277</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">C12/C11-1</f>
-        <v>0.217183770883055</v>
+        <v>0.365339578454333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19201,7 +19196,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -19221,6 +19216,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
@@ -19235,6 +19238,14 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
@@ -19247,6 +19258,14 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
@@ -19261,6 +19280,14 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
@@ -19293,6 +19320,14 @@
       <c r="J5" s="30" t="s">
         <v>572</v>
       </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
@@ -19326,6 +19361,14 @@
         <f aca="false">I6/G6</f>
         <v>1.44132397191575</v>
       </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
@@ -19359,6 +19402,14 @@
         <f aca="false">I7/G7</f>
         <v>1.42384769539078</v>
       </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
@@ -19392,6 +19443,14 @@
         <f aca="false">I8/G8</f>
         <v>1.42099898063201</v>
       </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
@@ -19425,6 +19484,14 @@
         <f aca="false">I9/G9</f>
         <v>1.423</v>
       </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
@@ -19458,6 +19525,14 @@
         <f aca="false">I10/G10</f>
         <v>1.43849206349206</v>
       </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
@@ -19499,6 +19574,14 @@
         <f aca="false">AVERAGE(J6:J10)</f>
         <v>1.42953254228612</v>
       </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
@@ -19537,6 +19620,14 @@
         <v>0.0401721664275465</v>
       </c>
       <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
@@ -19551,6 +19642,14 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -19563,6 +19662,14 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
@@ -19577,6 +19684,14 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
@@ -19607,6 +19722,14 @@
         <v>51</v>
       </c>
       <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
@@ -19637,6 +19760,14 @@
         <v>50.1</v>
       </c>
       <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
@@ -19667,6 +19798,14 @@
         <v>8.8</v>
       </c>
       <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
@@ -19697,6 +19836,14 @@
         <v>49.1</v>
       </c>
       <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
@@ -19727,6 +19874,14 @@
         <v>7.2</v>
       </c>
       <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
@@ -19757,6 +19912,14 @@
         <v>6.9</v>
       </c>
       <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
@@ -19787,6 +19950,14 @@
         <v>21.6</v>
       </c>
       <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -19799,6 +19970,14 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
@@ -19813,6 +19992,14 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
@@ -19835,6 +20022,14 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
@@ -19858,6 +20053,14 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
@@ -19881,6 +20084,14 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
@@ -19904,6 +20115,14 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
@@ -19927,6 +20146,14 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
@@ -19950,6 +20177,14 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
@@ -19973,6 +20208,14 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
@@ -19995,6 +20238,14 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
@@ -20017,6 +20268,14 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
@@ -20039,6 +20298,14 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
@@ -20061,6 +20328,14 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
@@ -20083,6 +20358,14 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
@@ -20097,6 +20380,14 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -20109,6 +20400,14 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
@@ -20123,6 +20422,14 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
@@ -20137,297 +20444,491 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
         <v>444</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="I41" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="30" t="s">
-        <v>51</v>
+        <v>592</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>593</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="L41" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="M41" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="N41" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="O41" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="P41" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q41" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="R41" s="29" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="B42" s="38" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="C42" s="39" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="D42" s="38" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="E42" s="38" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="F42" s="38" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="G42" s="38" t="n">
+        <v>599</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="39" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J42" s="39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" s="38" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N42" s="38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P42" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="38" t="n">
-        <v>1</v>
+      <c r="R42" s="38" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>593</v>
-      </c>
-      <c r="B43" s="38" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="C43" s="38" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="D43" s="39" t="n">
-        <v>0.833</v>
+        <v>600</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>-10</v>
       </c>
       <c r="E43" s="38" t="n">
-        <v>0.945</v>
+        <v>0.27</v>
       </c>
       <c r="F43" s="38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="39" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J43" s="39" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M43" s="38" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N43" s="38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="38" t="n">
+      <c r="R43" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>594</v>
-      </c>
-      <c r="B44" s="38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C44" s="38" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="D44" s="38" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="E44" s="39" t="n">
-        <v>0.889</v>
+        <v>601</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>0.23</v>
       </c>
       <c r="F44" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="39" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J44" s="39" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M44" s="38" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N44" s="38" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="38" t="n">
+      <c r="R44" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="B45" s="38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="C45" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="D45" s="38" t="n">
-        <v>0.417</v>
+        <v>602</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>-10</v>
       </c>
       <c r="E45" s="38" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="F45" s="39" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="G45" s="38" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="H45" s="38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" s="38" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N45" s="38" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O45" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="38" t="n">
+      <c r="R45" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>596</v>
-      </c>
-      <c r="B46" s="38" t="n">
+        <v>603</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F46" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="38" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F46" s="38" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="H46" s="38" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="I46" s="38" t="n">
+      <c r="G46" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J46" s="39" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K46" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M46" s="38" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N46" s="38" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O46" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="38" t="n">
+      <c r="R46" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="B47" s="38" t="n">
+        <v>604</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F47" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="38" t="n">
+      <c r="G47" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H47" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="38" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="F47" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="G47" s="38" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="H47" s="39" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="I47" s="38" t="n">
+      <c r="I47" s="39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J47" s="39" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" s="38" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N47" s="38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O47" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="P47" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="38" t="n">
+      <c r="R47" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>598</v>
-      </c>
-      <c r="B48" s="38" t="n">
+        <v>605</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F48" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C48" s="38" t="n">
+      <c r="G48" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="38" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G48" s="38" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="H48" s="38" t="n">
-        <v>0.445</v>
-      </c>
       <c r="I48" s="39" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="J48" s="38" t="n">
-        <v>0.972</v>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" s="38" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N48" s="38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>599</v>
-      </c>
-      <c r="B49" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>0</v>
+        <v>606</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>-10</v>
       </c>
       <c r="E49" s="38" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F49" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="38" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="H49" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="I49" s="38" t="n">
-        <v>0.444</v>
+      <c r="G49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>0.77</v>
       </c>
       <c r="J49" s="39" t="n">
-        <v>0.889</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
+      <c r="A50" s="6" t="s">
+        <v>607</v>
+      </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -20437,586 +20938,14 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="29" t="s">
-        <v>444</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G53" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="H53" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="I53" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="J53" s="30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="B54" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="C54" s="39" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="D54" s="38" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="F54" s="38" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="G54" s="38" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="H54" s="38" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="I54" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
-        <v>593</v>
-      </c>
-      <c r="B55" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="C55" s="38" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="D55" s="39" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="E55" s="38" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="F55" s="38" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="G55" s="38" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="H55" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
-        <v>594</v>
-      </c>
-      <c r="B56" s="38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="C56" s="38" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="D56" s="38" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="E56" s="39" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="F56" s="38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G56" s="38" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="H56" s="38" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="I56" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="B57" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="38" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="D57" s="38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="E57" s="38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F57" s="39" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="G57" s="38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="H57" s="38" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="I57" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="38" t="n">
-        <v>0.972</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
-        <v>596</v>
-      </c>
-      <c r="B58" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="38" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="E58" s="38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F58" s="38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="G58" s="39" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="H58" s="38" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I58" s="38" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="J58" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="B59" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="F59" s="38" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G59" s="38" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="H59" s="39" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="I59" s="38" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="J59" s="38" t="n">
-        <v>0.889</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
-        <v>598</v>
-      </c>
-      <c r="B60" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="38" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G60" s="38" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="H60" s="38" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="I60" s="39" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="J60" s="38" t="n">
-        <v>0.722</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="s">
-        <v>599</v>
-      </c>
-      <c r="B61" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="38" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="H61" s="38" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="I61" s="38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="J61" s="39" t="n">
-        <v>0.528</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="29" t="s">
-        <v>444</v>
-      </c>
-      <c r="B64" s="29" t="s">
-        <v>602</v>
-      </c>
-      <c r="C64" s="29" t="s">
-        <v>603</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>604</v>
-      </c>
-      <c r="E64" s="29" t="s">
-        <v>605</v>
-      </c>
-      <c r="F64" s="29" t="s">
-        <v>606</v>
-      </c>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" s="38" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D65" s="38" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E65" s="40" t="n">
-        <f aca="false">C65-D65</f>
-        <v>0.42</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C66" s="38" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D66" s="38" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E66" s="40" t="n">
-        <f aca="false">C66-D66</f>
-        <v>0.36</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C67" s="38" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="D67" s="38" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="E67" s="40" t="n">
-        <f aca="false">C67-D67</f>
-        <v>0.33</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C68" s="38" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D68" s="38" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E68" s="40" t="n">
-        <f aca="false">C68-D68</f>
-        <v>0.33</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C69" s="38" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D69" s="38" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E69" s="40" t="n">
-        <f aca="false">C69-D69</f>
-        <v>0.39</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" s="38" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D70" s="38" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E70" s="40" t="n">
-        <f aca="false">C70-D70</f>
-        <v>0.31</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>610</v>
-      </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C71" s="38" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D71" s="38" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E71" s="40" t="n">
-        <f aca="false">C71-D71</f>
-        <v>0.33</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
-        <v>468</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" s="38" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="D72" s="38" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E72" s="40" t="n">
-        <f aca="false">C72-D72</f>
-        <v>0.36</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/equipment_db.xlsx
+++ b/docs/equipment_db.xlsx
@@ -352,7 +352,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="590">
   <si>
     <r>
       <rPr>
@@ -4138,7 +4138,7 @@
     <t xml:space="preserve">s1pow</t>
   </si>
   <si>
-    <t xml:space="preserve">① 스킬 위력</t>
+    <t xml:space="preserve">① 갑옷 스킬 위력</t>
   </si>
   <si>
     <r>
@@ -4180,7 +4180,7 @@
     <t xml:space="preserve">s2pow</t>
   </si>
   <si>
-    <t xml:space="preserve">② 스킬 위력</t>
+    <t xml:space="preserve">② 무기 스킬 위력</t>
   </si>
   <si>
     <r>
@@ -4605,7 +4605,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 도발 중 받는 피해 감소 </t>
+      <t xml:space="preserve">② 돌진 베기 적중 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초간 받는 피해 감소 </t>
     </r>
     <r>
       <rPr>
@@ -4771,7 +4788,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 도발 지속 </t>
+      <t xml:space="preserve">① 맹세의 외침 도발 지속 </t>
     </r>
     <r>
       <rPr>
@@ -4861,7 +4878,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반사</t>
+      <t xml:space="preserve">되돌림</t>
     </r>
   </si>
   <si>
@@ -4898,7 +4915,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 급소 베기 출혈 피해 </t>
+      <t xml:space="preserve">출혈 피해 </t>
     </r>
     <r>
       <rPr>
@@ -4988,7 +5005,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 회전 베기 범위 </t>
+      <t xml:space="preserve">② 그림자 연격 위력 </t>
     </r>
     <r>
       <rPr>
@@ -5095,7 +5112,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 회전 베기 쿨타임 </t>
+      <t xml:space="preserve">① 발목 베기 쿨타임 </t>
     </r>
     <r>
       <rPr>
@@ -5140,7 +5157,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">출혈 걸린 적에게 피해 </t>
+      <t xml:space="preserve">출혈 중인 적에게 피해 </t>
     </r>
     <r>
       <rPr>
@@ -5200,7 +5217,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 관통 사격 취약 지속 </t>
+      <t xml:space="preserve">취약 지속 </t>
     </r>
     <r>
       <rPr>
@@ -5253,7 +5270,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">평타 </t>
+      <t xml:space="preserve">평타가 </t>
     </r>
     <r>
       <rPr>
@@ -5323,7 +5340,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 집중 사격 위력 </t>
+      <t xml:space="preserve">② 저격 위력 </t>
     </r>
     <r>
       <rPr>
@@ -5368,7 +5385,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 화살비 범위 </t>
+      <t xml:space="preserve">① 관통 사격 위력 </t>
     </r>
     <r>
       <rPr>
@@ -5410,24 +5427,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">적이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70px </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안에 있으면 받는 피해 </t>
+      <t xml:space="preserve">가까이 붙은 적이 있으면 받는 피해 </t>
     </r>
     <r>
       <rPr>
@@ -5549,7 +5549,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 별빛 탄 화상 피해 </t>
+      <t xml:space="preserve">화상 피해 </t>
     </r>
     <r>
       <rPr>
@@ -5594,7 +5594,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 유성우 범위 </t>
+      <t xml:space="preserve">② 번개 사슬 위력 </t>
     </r>
     <r>
       <rPr>
@@ -5636,7 +5636,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 대마법이 그로기 적에게 위력 </t>
+      <t xml:space="preserve">③ 필살기가 그로기 적에게 주는 피해 </t>
     </r>
     <r>
       <rPr>
@@ -5847,7 +5847,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 치유 회복량 </t>
+      <t xml:space="preserve">② 광역 치유 회복량 </t>
     </r>
     <r>
       <rPr>
@@ -5892,7 +5892,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 광역 치유 범위 </t>
+      <t xml:space="preserve">② 빛의 심판 위력 </t>
     </r>
     <r>
       <rPr>
@@ -5934,7 +5934,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">치유받은 아군 </t>
+      <t xml:space="preserve">회복받은 아군은 </t>
     </r>
     <r>
       <rPr>
@@ -5996,7 +5996,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파티 회복 받는 양 </t>
+      <t xml:space="preserve">파티가 받는 회복량 </t>
     </r>
     <r>
       <rPr>
@@ -6041,7 +6041,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 생명의 나무 지속 </t>
+      <t xml:space="preserve">① 수호의 기도 공명 지속 </t>
     </r>
     <r>
       <rPr>
@@ -8097,6 +8097,42 @@
     <t xml:space="preserve">s1_power</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① 도발 중 받는 피해 감소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]%p</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">s1_cd</t>
   </si>
   <si>
@@ -8106,7 +8142,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 도발 쿨타임 </t>
+      <t xml:space="preserve">① 갑옷 스킬 쿨타임 </t>
     </r>
     <r>
       <rPr>
@@ -8145,7 +8181,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 방패 강타 위력 </t>
+      <t xml:space="preserve">② 무기 스킬 위력 </t>
     </r>
     <r>
       <rPr>
@@ -8181,7 +8217,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">② 방패 강타 쿨타임 </t>
+      <t xml:space="preserve">② 무기 스킬 쿨타임 </t>
     </r>
     <r>
       <rPr>
@@ -8217,7 +8253,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 철벽 피해 감소 </t>
+      <t xml:space="preserve">③ 필살기 효과 </t>
     </r>
     <r>
       <rPr>
@@ -8253,7 +8289,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 철벽 지속 </t>
+      <t xml:space="preserve">③ 필살기 지속 </t>
     </r>
     <r>
       <rPr>
@@ -8297,7 +8333,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 급소 베기 위력 </t>
+      <t xml:space="preserve">① 갑옷 스킬 위력 </t>
     </r>
     <r>
       <rPr>
@@ -8333,16 +8369,16 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 급소 베기 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
+      <t xml:space="preserve">③ 필살기 위력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
     </r>
     <r>
       <rPr>
@@ -8363,13 +8399,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 회전 베기 위력 </t>
+    <t xml:space="preserve">ult_hits</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 필살기 타수 </t>
     </r>
     <r>
       <rPr>
@@ -8395,6 +8434,48 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ult_gain</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 필살기 충전 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">]%</t>
     </r>
   </si>
@@ -8405,7 +8486,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">③ 난도질 위력 </t>
+      <t xml:space="preserve">① 갑옷 스킬 위력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
     </r>
     <r>
       <rPr>
@@ -8435,16 +8533,30 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ult_hits</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 난도질 타수 </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">② 무기 스킬 위력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
     </r>
     <r>
       <rPr>
@@ -8470,20 +8582,34 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 관통 사격 위력 </t>
+      <t xml:space="preserve">]%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 필살기 위력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
     </r>
     <r>
       <rPr>
@@ -8493,708 +8619,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 관통 사격 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 화살비 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 화살비 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ult_gain</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 필살기 충전 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 별빛 탄 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 별빛 탄 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 유성우 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 유성우 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 대마법 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 치유 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 광역 치유 회복량 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 광역 치유 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 생명의 나무 회복량 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 기본 스킬 위력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 상황 스킬 위력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 필살기 위력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 기본 스킬 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">② 상황 스킬 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-[</t>
     </r>
     <r>
       <rPr>
@@ -9510,12 +8934,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">① 기본 스킬 위력</t>
-  </si>
-  <si>
-    <t xml:space="preserve">② 상황 스킬 위력</t>
-  </si>
-  <si>
     <t xml:space="preserve">③ 필살기 위력</t>
   </si>
   <si>
@@ -10216,7 +9634,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일반 전투 보상</t>
+      <t xml:space="preserve">일반 전투 보상 </t>
     </r>
     <r>
       <rPr>
@@ -10254,7 +9672,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">중 장비 카드</t>
+      <t xml:space="preserve">장비 카드</t>
     </r>
     <r>
       <rPr>
@@ -10673,7 +10091,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보스 처치</t>
+      <t xml:space="preserve">보스 처치 </t>
     </r>
     <r>
       <rPr>
@@ -11404,6 +10822,99 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">간 무적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter_rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">여우비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적이 그로기가 되면 ② 무기 스킬 쿨타임 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">] </t>
     </r>
     <r>
@@ -11412,75 +10923,110 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">무적 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전투당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter_rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">여우비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적이 그로기에 빠지면 ② 쿨타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
+      <t xml:space="preserve">감소</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">old_root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늙은 참나무의 뿌리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트레이드오프</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이동 속도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">berserk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광전사의 피</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받는 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">moon_oath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 맹세</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그로기가 아닌 큰 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">first_light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숲의 첫 숨</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필살기 위력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+[</t>
     </r>
     <r>
       <rPr>
@@ -11497,139 +11043,11 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">감소</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">old_root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">늙은 참나무의 뿌리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트레이드오프</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이동 속도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">berserk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광전사의 피</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받는 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+12%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">moon_oath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">달빛 맹세</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그로기 게이지가 있는 적이 그로기가 아닐 때 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">first_light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">숲의 첫 숨</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필살기 위력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">]</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">필살기 게이지는 그로기 적이 있을 때만 참</t>
+    <t xml:space="preserve">필살기 게이지는 그로기 적이 있을 때만 충전</t>
   </si>
   <si>
     <t xml:space="preserve">장비 강화</t>
@@ -14813,7 +14231,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14825,7 +14243,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14847,28 +14265,28 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14876,14 +14294,14 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">C5</f>
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>43</v>
@@ -14903,7 +14321,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>1.42</v>
@@ -14923,7 +14341,7 @@
       </c>
       <c r="H6" s="11" t="n">
         <f aca="false">C6/C5-1</f>
-        <v>0.126984126984127</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14931,7 +14349,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>1.67</v>
@@ -14959,7 +14377,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2.28</v>
@@ -14987,7 +14405,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>2.55</v>
@@ -15015,7 +14433,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>3.28</v>
@@ -15043,7 +14461,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>4.27</v>
@@ -15071,7 +14489,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>5.83</v>
@@ -15106,7 +14524,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -15142,7 +14560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15163,7 +14581,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15203,7 +14621,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -15224,60 +14642,60 @@
     </row>
     <row r="5" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="O5" s="34" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>75.81</v>
@@ -15338,7 +14756,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>88.42</v>
@@ -15399,7 +14817,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>22.15</v>
@@ -15460,7 +14878,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>1.19</v>
@@ -15521,7 +14939,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>0.01</v>
@@ -15582,7 +15000,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>0</v>
@@ -15643,7 +15061,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>0</v>
@@ -15704,7 +15122,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>0</v>
@@ -15784,7 +15202,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -15805,60 +15223,60 @@
     </row>
     <row r="16" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="N16" s="34" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="P16" s="34" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="Q16" s="34" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>88.42</v>
@@ -15919,7 +15337,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>22.15</v>
@@ -15980,7 +15398,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>1.19</v>
@@ -16041,7 +15459,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>0.01</v>
@@ -16102,7 +15520,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>0</v>
@@ -16163,7 +15581,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>0</v>
@@ -16224,7 +15642,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>0</v>
@@ -16285,7 +15703,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>0</v>
@@ -16365,7 +15783,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -16386,60 +15804,60 @@
     </row>
     <row r="27" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I27" s="34" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="J27" s="34" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="K27" s="34" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="L27" s="34" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="M27" s="34" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="N27" s="34" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="O27" s="34" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="P27" s="34" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="Q27" s="34" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>46.34</v>
@@ -16500,7 +15918,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>4.61</v>
@@ -16561,7 +15979,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>0.1</v>
@@ -16622,7 +16040,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>0</v>
@@ -16683,7 +16101,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>0</v>
@@ -16744,7 +16162,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>0</v>
@@ -16805,7 +16223,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>0</v>
@@ -16866,7 +16284,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="B35" s="9" t="n">
         <v>0</v>
@@ -16946,7 +16364,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -16967,60 +16385,60 @@
     </row>
     <row r="38" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H38" s="34" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I38" s="34" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="K38" s="34" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="L38" s="34" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="M38" s="34" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="N38" s="34" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="O38" s="34" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="P38" s="34" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="Q38" s="34" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>46.34</v>
@@ -17081,7 +16499,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>100</v>
@@ -17142,7 +16560,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B41" s="9" t="n">
         <v>46.34</v>
@@ -17203,7 +16621,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B42" s="9" t="n">
         <v>4.61</v>
@@ -17264,7 +16682,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>0.1</v>
@@ -17325,7 +16743,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B44" s="9" t="n">
         <v>0</v>
@@ -17386,7 +16804,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>0</v>
@@ -17447,7 +16865,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="B46" s="9" t="n">
         <v>0</v>
@@ -17536,7 +16954,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17555,7 +16973,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17574,28 +16992,28 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>25</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>35</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>25</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="I3" s="10" t="n">
         <v>15</v>
@@ -17615,7 +17033,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="35" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>1</v>
@@ -17650,19 +17068,19 @@
         <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>357</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>43</v>
@@ -17691,19 +17109,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="F6" s="31" t="n">
         <v>0.03</v>
@@ -17744,19 +17162,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>0.02</v>
@@ -17797,19 +17215,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>0.06</v>
@@ -17850,19 +17268,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>0.025</v>
@@ -17902,19 +17320,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>0.02</v>
@@ -17954,19 +17372,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>0.06</v>
@@ -18005,19 +17423,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>0.025</v>
@@ -18056,19 +17474,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>0.06</v>
@@ -18107,16 +17525,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>221</v>
@@ -18157,19 +17575,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>10</v>
@@ -18207,19 +17625,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>1</v>
@@ -18256,19 +17674,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>0.2</v>
@@ -18305,25 +17723,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>0.08</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>78</v>
@@ -18355,25 +17773,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>0.06</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>78</v>
@@ -18405,25 +17823,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>0.16</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>78</v>
@@ -18454,25 +17872,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>0.13</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>78</v>
@@ -18529,7 +17947,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18541,7 +17959,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18553,19 +17971,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="B3" s="37" t="n">
         <v>0.06</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F3" s="31" t="n">
         <v>0.465</v>
@@ -18585,33 +18003,33 @@
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>1</v>
@@ -18638,7 +18056,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>1</v>
@@ -18665,7 +18083,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>0.95</v>
@@ -18692,7 +18110,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0.9</v>
@@ -18719,7 +18137,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>0.85</v>
@@ -18743,12 +18161,12 @@
         <v>3</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>0.75</v>
@@ -18775,7 +18193,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>0.65</v>
@@ -18802,7 +18220,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>0.55</v>
@@ -18829,7 +18247,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>0.45</v>
@@ -18856,7 +18274,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>0.35</v>
@@ -18880,12 +18298,12 @@
         <v>4</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="B16" s="14" t="n">
         <v>0.25</v>
@@ -18912,7 +18330,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>0.18</v>
@@ -18939,7 +18357,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="B18" s="14" t="n">
         <v>0.12</v>
@@ -18966,7 +18384,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>0.08</v>
@@ -18993,7 +18411,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>0.05</v>
@@ -19017,7 +18435,7 @@
         <v>22</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19032,7 +18450,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -19106,7 +18524,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -19170,7 +18588,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -19205,7 +18623,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19227,7 +18645,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -19269,7 +18687,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19318,7 +18736,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -19536,7 +18954,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="false">AVERAGE(B6:B10)</f>
@@ -19585,7 +19003,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">MAX(B6:B10)/MIN(B6:B10)-1</f>
@@ -19631,7 +19049,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -19673,7 +19091,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -19695,7 +19113,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>43</v>
@@ -19733,7 +19151,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>15.2</v>
@@ -19809,7 +19227,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="B19" s="17" t="n">
         <v>0</v>
@@ -19923,7 +19341,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="B22" s="17" t="n">
         <v>0</v>
@@ -19981,7 +19399,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -20006,16 +19424,16 @@
         <v>66</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="C25" s="29" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -20046,7 +19464,7 @@
         <v>초과 → 상한 적용</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -20077,7 +19495,7 @@
         <v>초과 → 상한 적용</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -20108,7 +19526,7 @@
         <v>초과 → 상한 적용</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -20139,7 +19557,7 @@
         <v>OK</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -20170,7 +19588,7 @@
         <v>초과 → 상한 적용</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -20201,7 +19619,7 @@
         <v>초과 → 상한 적용</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -20228,10 +19646,10 @@
         <v>78</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -20258,10 +19676,10 @@
         <v>78</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -20288,10 +19706,10 @@
         <v>78</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -20318,10 +19736,10 @@
         <v>78</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -20348,10 +19766,10 @@
         <v>78</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -20369,7 +19787,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -20411,7 +19829,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -20433,7 +19851,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -20455,63 +19873,63 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="E41" s="29" t="s">
         <v>139</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="G41" s="29" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>139</v>
       </c>
       <c r="J41" s="29" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="K41" s="29" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="L41" s="29" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="M41" s="29" t="s">
         <v>139</v>
       </c>
       <c r="N41" s="29" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="O41" s="29" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="P41" s="29" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="Q41" s="29" t="s">
         <v>139</v>
       </c>
       <c r="R41" s="29" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="B42" s="9" t="n">
         <v>1.26</v>
@@ -20559,7 +19977,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>1.42</v>
@@ -20615,7 +20033,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="B44" s="9" t="n">
         <v>1.67</v>
@@ -20671,7 +20089,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>2.28</v>
@@ -20727,7 +20145,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B46" s="9" t="n">
         <v>2.55</v>
@@ -20783,7 +20201,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="B47" s="9" t="n">
         <v>3.28</v>
@@ -20839,7 +20257,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="B48" s="9" t="n">
         <v>4.27</v>
@@ -20887,7 +20305,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="B49" s="9" t="n">
         <v>5.83</v>
@@ -20927,7 +20345,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -24903,7 +24321,7 @@
       </c>
       <c r="I13" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J13" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D13,등급!$A$5:$A$12,0)),1)</f>
@@ -24960,7 +24378,7 @@
       </c>
       <c r="I14" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J14" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D14,등급!$A$5:$A$12,0)),1)</f>
@@ -25017,7 +24435,7 @@
       </c>
       <c r="I15" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D15,등급!$A$5:$A$12,0)),1)</f>
@@ -25074,7 +24492,7 @@
       </c>
       <c r="I16" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J16" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D16,등급!$A$5:$A$12,0)),1)</f>
@@ -25131,7 +24549,7 @@
       </c>
       <c r="I17" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J17" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D17,등급!$A$5:$A$12,0)),1)</f>
@@ -25188,7 +24606,7 @@
       </c>
       <c r="I18" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J18" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D18,등급!$A$5:$A$12,0)),1)</f>
@@ -25245,7 +24663,7 @@
       </c>
       <c r="I19" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J19" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D19,등급!$A$5:$A$12,0)),1)</f>
@@ -25302,7 +24720,7 @@
       </c>
       <c r="I20" s="19" t="str">
         <f aca="false">장비_기본!J6</f>
-        <v>① 도발 중 받는 피해 감소 +[값]%p</v>
+        <v>② 돌진 베기 적중 후 3초간 받는 피해 감소 +[값]%p</v>
       </c>
       <c r="J20" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K6*INDEX(등급!$F$5:$F$12,MATCH($D20,등급!$A$5:$A$12,0)),1)</f>
@@ -26271,7 +25689,7 @@
       </c>
       <c r="I37" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J37" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D37,등급!$A$5:$A$12,0)),1)</f>
@@ -26328,7 +25746,7 @@
       </c>
       <c r="I38" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J38" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D38,등급!$A$5:$A$12,0)),1)</f>
@@ -26385,7 +25803,7 @@
       </c>
       <c r="I39" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J39" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D39,등급!$A$5:$A$12,0)),1)</f>
@@ -26442,7 +25860,7 @@
       </c>
       <c r="I40" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J40" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D40,등급!$A$5:$A$12,0)),1)</f>
@@ -26499,7 +25917,7 @@
       </c>
       <c r="I41" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J41" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D41,등급!$A$5:$A$12,0)),1)</f>
@@ -26556,7 +25974,7 @@
       </c>
       <c r="I42" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J42" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D42,등급!$A$5:$A$12,0)),1)</f>
@@ -26613,7 +26031,7 @@
       </c>
       <c r="I43" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J43" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D43,등급!$A$5:$A$12,0)),1)</f>
@@ -26670,7 +26088,7 @@
       </c>
       <c r="I44" s="19" t="str">
         <f aca="false">장비_기본!J9</f>
-        <v>① 도발 지속 +[값]초</v>
+        <v>① 맹세의 외침 도발 지속 +[값]초</v>
       </c>
       <c r="J44" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K9*INDEX(등급!$F$5:$F$12,MATCH($D44,등급!$A$5:$A$12,0)),1)</f>
@@ -26727,7 +26145,7 @@
       </c>
       <c r="I45" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J45" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D45,등급!$A$5:$A$12,0)),1)</f>
@@ -26784,7 +26202,7 @@
       </c>
       <c r="I46" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J46" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D46,등급!$A$5:$A$12,0)),1)</f>
@@ -26841,7 +26259,7 @@
       </c>
       <c r="I47" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J47" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D47,등급!$A$5:$A$12,0)),1)</f>
@@ -26898,7 +26316,7 @@
       </c>
       <c r="I48" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J48" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D48,등급!$A$5:$A$12,0)),1)</f>
@@ -26955,7 +26373,7 @@
       </c>
       <c r="I49" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J49" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D49,등급!$A$5:$A$12,0)),1)</f>
@@ -27012,7 +26430,7 @@
       </c>
       <c r="I50" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J50" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D50,등급!$A$5:$A$12,0)),1)</f>
@@ -27069,7 +26487,7 @@
       </c>
       <c r="I51" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J51" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D51,등급!$A$5:$A$12,0)),1)</f>
@@ -27126,7 +26544,7 @@
       </c>
       <c r="I52" s="19" t="str">
         <f aca="false">장비_기본!J10</f>
-        <v>받은 근접 피해의 [값]% 반사</v>
+        <v>받은 근접 피해의 [값]% 되돌림</v>
       </c>
       <c r="J52" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K10*INDEX(등급!$F$5:$F$12,MATCH($D52,등급!$A$5:$A$12,0)),1)</f>
@@ -27175,7 +26593,7 @@
       </c>
       <c r="G53" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H53" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D53,등급!$A$5:$A$12,0))</f>
@@ -27228,7 +26646,7 @@
       </c>
       <c r="G54" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H54" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D54,등급!$A$5:$A$12,0))</f>
@@ -27281,7 +26699,7 @@
       </c>
       <c r="G55" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H55" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D55,등급!$A$5:$A$12,0))</f>
@@ -27334,7 +26752,7 @@
       </c>
       <c r="G56" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H56" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D56,등급!$A$5:$A$12,0))</f>
@@ -27387,7 +26805,7 @@
       </c>
       <c r="G57" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H57" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D57,등급!$A$5:$A$12,0))</f>
@@ -27440,7 +26858,7 @@
       </c>
       <c r="G58" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H58" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D58,등급!$A$5:$A$12,0))</f>
@@ -27493,7 +26911,7 @@
       </c>
       <c r="G59" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H59" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D59,등급!$A$5:$A$12,0))</f>
@@ -27546,7 +26964,7 @@
       </c>
       <c r="G60" s="19" t="str">
         <f aca="false">장비_기본!H11</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H60" s="21" t="n">
         <f aca="false">장비_기본!I11*INDEX(등급!$C$5:$C$12,MATCH($D60,등급!$A$5:$A$12,0))</f>
@@ -27599,7 +27017,7 @@
       </c>
       <c r="G61" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H61" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D61,등급!$A$5:$A$12,0))</f>
@@ -27652,7 +27070,7 @@
       </c>
       <c r="G62" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H62" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D62,등급!$A$5:$A$12,0))</f>
@@ -27705,7 +27123,7 @@
       </c>
       <c r="G63" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H63" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D63,등급!$A$5:$A$12,0))</f>
@@ -27758,7 +27176,7 @@
       </c>
       <c r="G64" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H64" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D64,등급!$A$5:$A$12,0))</f>
@@ -27811,7 +27229,7 @@
       </c>
       <c r="G65" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H65" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D65,등급!$A$5:$A$12,0))</f>
@@ -27864,7 +27282,7 @@
       </c>
       <c r="G66" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H66" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D66,등급!$A$5:$A$12,0))</f>
@@ -27917,7 +27335,7 @@
       </c>
       <c r="G67" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H67" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D67,등급!$A$5:$A$12,0))</f>
@@ -27970,7 +27388,7 @@
       </c>
       <c r="G68" s="19" t="str">
         <f aca="false">장비_기본!H12</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H68" s="21" t="n">
         <f aca="false">장비_기본!I12*INDEX(등급!$C$5:$C$12,MATCH($D68,등급!$A$5:$A$12,0))</f>
@@ -28031,7 +27449,7 @@
       </c>
       <c r="I69" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J69" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D69,등급!$A$5:$A$12,0)),1)</f>
@@ -28088,7 +27506,7 @@
       </c>
       <c r="I70" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J70" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D70,등급!$A$5:$A$12,0)),1)</f>
@@ -28145,7 +27563,7 @@
       </c>
       <c r="I71" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J71" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D71,등급!$A$5:$A$12,0)),1)</f>
@@ -28202,7 +27620,7 @@
       </c>
       <c r="I72" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J72" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D72,등급!$A$5:$A$12,0)),1)</f>
@@ -28259,7 +27677,7 @@
       </c>
       <c r="I73" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J73" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D73,등급!$A$5:$A$12,0)),1)</f>
@@ -28316,7 +27734,7 @@
       </c>
       <c r="I74" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J74" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D74,등급!$A$5:$A$12,0)),1)</f>
@@ -28373,7 +27791,7 @@
       </c>
       <c r="I75" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J75" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D75,등급!$A$5:$A$12,0)),1)</f>
@@ -28430,7 +27848,7 @@
       </c>
       <c r="I76" s="19" t="str">
         <f aca="false">장비_기본!J13</f>
-        <v>① 급소 베기 출혈 피해 +[값]%</v>
+        <v>출혈 피해 +[값]%</v>
       </c>
       <c r="J76" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K13*INDEX(등급!$F$5:$F$12,MATCH($D76,등급!$A$5:$A$12,0)),1)</f>
@@ -28943,7 +28361,7 @@
       </c>
       <c r="I85" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J85" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D85,등급!$A$5:$A$12,0)),1)</f>
@@ -29000,7 +28418,7 @@
       </c>
       <c r="I86" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J86" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D86,등급!$A$5:$A$12,0)),1)</f>
@@ -29057,7 +28475,7 @@
       </c>
       <c r="I87" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J87" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D87,등급!$A$5:$A$12,0)),1)</f>
@@ -29114,7 +28532,7 @@
       </c>
       <c r="I88" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J88" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D88,등급!$A$5:$A$12,0)),1)</f>
@@ -29171,7 +28589,7 @@
       </c>
       <c r="I89" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J89" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D89,등급!$A$5:$A$12,0)),1)</f>
@@ -29228,7 +28646,7 @@
       </c>
       <c r="I90" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J90" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D90,등급!$A$5:$A$12,0)),1)</f>
@@ -29285,7 +28703,7 @@
       </c>
       <c r="I91" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J91" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D91,등급!$A$5:$A$12,0)),1)</f>
@@ -29342,7 +28760,7 @@
       </c>
       <c r="I92" s="19" t="str">
         <f aca="false">장비_기본!J15</f>
-        <v>② 회전 베기 범위 +[값]%</v>
+        <v>② 그림자 연격 위력 +[값]%</v>
       </c>
       <c r="J92" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K15*INDEX(등급!$F$5:$F$12,MATCH($D92,등급!$A$5:$A$12,0)),1)</f>
@@ -29855,7 +29273,7 @@
       </c>
       <c r="I101" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J101" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D101,등급!$A$5:$A$12,0)),1)</f>
@@ -29912,7 +29330,7 @@
       </c>
       <c r="I102" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J102" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D102,등급!$A$5:$A$12,0)),1)</f>
@@ -29969,7 +29387,7 @@
       </c>
       <c r="I103" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J103" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D103,등급!$A$5:$A$12,0)),1)</f>
@@ -30026,7 +29444,7 @@
       </c>
       <c r="I104" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J104" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D104,등급!$A$5:$A$12,0)),1)</f>
@@ -30083,7 +29501,7 @@
       </c>
       <c r="I105" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J105" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D105,등급!$A$5:$A$12,0)),1)</f>
@@ -30140,7 +29558,7 @@
       </c>
       <c r="I106" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J106" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D106,등급!$A$5:$A$12,0)),1)</f>
@@ -30197,7 +29615,7 @@
       </c>
       <c r="I107" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J107" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D107,등급!$A$5:$A$12,0)),1)</f>
@@ -30254,7 +29672,7 @@
       </c>
       <c r="I108" s="19" t="str">
         <f aca="false">장비_기본!J17</f>
-        <v>② 회전 베기 쿨타임 -[값]%</v>
+        <v>① 발목 베기 쿨타임 -[값]%</v>
       </c>
       <c r="J108" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K17*INDEX(등급!$F$5:$F$12,MATCH($D108,등급!$A$5:$A$12,0)),1)</f>
@@ -30311,7 +29729,7 @@
       </c>
       <c r="I109" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J109" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D109,등급!$A$5:$A$12,0)),1)</f>
@@ -30368,7 +29786,7 @@
       </c>
       <c r="I110" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J110" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D110,등급!$A$5:$A$12,0)),1)</f>
@@ -30425,7 +29843,7 @@
       </c>
       <c r="I111" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J111" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D111,등급!$A$5:$A$12,0)),1)</f>
@@ -30482,7 +29900,7 @@
       </c>
       <c r="I112" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J112" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D112,등급!$A$5:$A$12,0)),1)</f>
@@ -30539,7 +29957,7 @@
       </c>
       <c r="I113" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J113" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D113,등급!$A$5:$A$12,0)),1)</f>
@@ -30596,7 +30014,7 @@
       </c>
       <c r="I114" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J114" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D114,등급!$A$5:$A$12,0)),1)</f>
@@ -30653,7 +30071,7 @@
       </c>
       <c r="I115" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J115" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D115,등급!$A$5:$A$12,0)),1)</f>
@@ -30710,7 +30128,7 @@
       </c>
       <c r="I116" s="19" t="str">
         <f aca="false">장비_기본!J18</f>
-        <v>출혈 걸린 적에게 피해 +[값]%</v>
+        <v>출혈 중인 적에게 피해 +[값]%</v>
       </c>
       <c r="J116" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K18*INDEX(등급!$F$5:$F$12,MATCH($D116,등급!$A$5:$A$12,0)),1)</f>
@@ -30759,7 +30177,7 @@
       </c>
       <c r="G117" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H117" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D117,등급!$A$5:$A$12,0))</f>
@@ -30812,7 +30230,7 @@
       </c>
       <c r="G118" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H118" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D118,등급!$A$5:$A$12,0))</f>
@@ -30865,7 +30283,7 @@
       </c>
       <c r="G119" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H119" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D119,등급!$A$5:$A$12,0))</f>
@@ -30918,7 +30336,7 @@
       </c>
       <c r="G120" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H120" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D120,등급!$A$5:$A$12,0))</f>
@@ -30971,7 +30389,7 @@
       </c>
       <c r="G121" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H121" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D121,등급!$A$5:$A$12,0))</f>
@@ -31024,7 +30442,7 @@
       </c>
       <c r="G122" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H122" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D122,등급!$A$5:$A$12,0))</f>
@@ -31077,7 +30495,7 @@
       </c>
       <c r="G123" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H123" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D123,등급!$A$5:$A$12,0))</f>
@@ -31130,7 +30548,7 @@
       </c>
       <c r="G124" s="19" t="str">
         <f aca="false">장비_기본!H19</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H124" s="21" t="n">
         <f aca="false">장비_기본!I19*INDEX(등급!$C$5:$C$12,MATCH($D124,등급!$A$5:$A$12,0))</f>
@@ -31183,7 +30601,7 @@
       </c>
       <c r="G125" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H125" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D125,등급!$A$5:$A$12,0))</f>
@@ -31236,7 +30654,7 @@
       </c>
       <c r="G126" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H126" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D126,등급!$A$5:$A$12,0))</f>
@@ -31289,7 +30707,7 @@
       </c>
       <c r="G127" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H127" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D127,등급!$A$5:$A$12,0))</f>
@@ -31342,7 +30760,7 @@
       </c>
       <c r="G128" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H128" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D128,등급!$A$5:$A$12,0))</f>
@@ -31395,7 +30813,7 @@
       </c>
       <c r="G129" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H129" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D129,등급!$A$5:$A$12,0))</f>
@@ -31448,7 +30866,7 @@
       </c>
       <c r="G130" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H130" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D130,등급!$A$5:$A$12,0))</f>
@@ -31501,7 +30919,7 @@
       </c>
       <c r="G131" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H131" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D131,등급!$A$5:$A$12,0))</f>
@@ -31554,7 +30972,7 @@
       </c>
       <c r="G132" s="19" t="str">
         <f aca="false">장비_기본!H20</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H132" s="21" t="n">
         <f aca="false">장비_기본!I20*INDEX(등급!$C$5:$C$12,MATCH($D132,등급!$A$5:$A$12,0))</f>
@@ -31615,7 +31033,7 @@
       </c>
       <c r="I133" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J133" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D133,등급!$A$5:$A$12,0)),1)</f>
@@ -31672,7 +31090,7 @@
       </c>
       <c r="I134" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J134" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D134,등급!$A$5:$A$12,0)),1)</f>
@@ -31729,7 +31147,7 @@
       </c>
       <c r="I135" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J135" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D135,등급!$A$5:$A$12,0)),1)</f>
@@ -31786,7 +31204,7 @@
       </c>
       <c r="I136" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J136" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D136,등급!$A$5:$A$12,0)),1)</f>
@@ -31843,7 +31261,7 @@
       </c>
       <c r="I137" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J137" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D137,등급!$A$5:$A$12,0)),1)</f>
@@ -31900,7 +31318,7 @@
       </c>
       <c r="I138" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J138" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D138,등급!$A$5:$A$12,0)),1)</f>
@@ -31957,7 +31375,7 @@
       </c>
       <c r="I139" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J139" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D139,등급!$A$5:$A$12,0)),1)</f>
@@ -32014,7 +31432,7 @@
       </c>
       <c r="I140" s="19" t="str">
         <f aca="false">장비_기본!J21</f>
-        <v>① 관통 사격 취약 지속 +[값]초</v>
+        <v>취약 지속 +[값]초</v>
       </c>
       <c r="J140" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K21*INDEX(등급!$F$5:$F$12,MATCH($D140,등급!$A$5:$A$12,0)),1)</f>
@@ -32071,7 +31489,7 @@
       </c>
       <c r="I141" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J141" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D141,등급!$A$5:$A$12,0)),1)</f>
@@ -32128,7 +31546,7 @@
       </c>
       <c r="I142" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J142" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D142,등급!$A$5:$A$12,0)),1)</f>
@@ -32185,7 +31603,7 @@
       </c>
       <c r="I143" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J143" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D143,등급!$A$5:$A$12,0)),1)</f>
@@ -32242,7 +31660,7 @@
       </c>
       <c r="I144" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J144" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D144,등급!$A$5:$A$12,0)),1)</f>
@@ -32299,7 +31717,7 @@
       </c>
       <c r="I145" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J145" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D145,등급!$A$5:$A$12,0)),1)</f>
@@ -32356,7 +31774,7 @@
       </c>
       <c r="I146" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J146" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D146,등급!$A$5:$A$12,0)),1)</f>
@@ -32413,7 +31831,7 @@
       </c>
       <c r="I147" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J147" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D147,등급!$A$5:$A$12,0)),1)</f>
@@ -32470,7 +31888,7 @@
       </c>
       <c r="I148" s="19" t="str">
         <f aca="false">장비_기본!J22</f>
-        <v>평타 [값]% 확률로 2연사</v>
+        <v>평타가 [값]% 확률로 2연사</v>
       </c>
       <c r="J148" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K22*INDEX(등급!$F$5:$F$12,MATCH($D148,등급!$A$5:$A$12,0)),1)</f>
@@ -32527,7 +31945,7 @@
       </c>
       <c r="I149" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J149" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D149,등급!$A$5:$A$12,0)),1)</f>
@@ -32584,7 +32002,7 @@
       </c>
       <c r="I150" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J150" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D150,등급!$A$5:$A$12,0)),1)</f>
@@ -32641,7 +32059,7 @@
       </c>
       <c r="I151" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J151" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D151,등급!$A$5:$A$12,0)),1)</f>
@@ -32698,7 +32116,7 @@
       </c>
       <c r="I152" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J152" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D152,등급!$A$5:$A$12,0)),1)</f>
@@ -32755,7 +32173,7 @@
       </c>
       <c r="I153" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J153" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D153,등급!$A$5:$A$12,0)),1)</f>
@@ -32812,7 +32230,7 @@
       </c>
       <c r="I154" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J154" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D154,등급!$A$5:$A$12,0)),1)</f>
@@ -32869,7 +32287,7 @@
       </c>
       <c r="I155" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J155" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D155,등급!$A$5:$A$12,0)),1)</f>
@@ -32926,7 +32344,7 @@
       </c>
       <c r="I156" s="19" t="str">
         <f aca="false">장비_기본!J23</f>
-        <v>③ 집중 사격 위력 +[값]%</v>
+        <v>② 저격 위력 +[값]%</v>
       </c>
       <c r="J156" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K23*INDEX(등급!$F$5:$F$12,MATCH($D156,등급!$A$5:$A$12,0)),1)</f>
@@ -32983,7 +32401,7 @@
       </c>
       <c r="I157" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J157" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D157,등급!$A$5:$A$12,0)),1)</f>
@@ -33040,7 +32458,7 @@
       </c>
       <c r="I158" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J158" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D158,등급!$A$5:$A$12,0)),1)</f>
@@ -33097,7 +32515,7 @@
       </c>
       <c r="I159" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J159" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D159,등급!$A$5:$A$12,0)),1)</f>
@@ -33154,7 +32572,7 @@
       </c>
       <c r="I160" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J160" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D160,등급!$A$5:$A$12,0)),1)</f>
@@ -33211,7 +32629,7 @@
       </c>
       <c r="I161" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J161" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D161,등급!$A$5:$A$12,0)),1)</f>
@@ -33268,7 +32686,7 @@
       </c>
       <c r="I162" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J162" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D162,등급!$A$5:$A$12,0)),1)</f>
@@ -33325,7 +32743,7 @@
       </c>
       <c r="I163" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J163" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D163,등급!$A$5:$A$12,0)),1)</f>
@@ -33382,7 +32800,7 @@
       </c>
       <c r="I164" s="19" t="str">
         <f aca="false">장비_기본!J24</f>
-        <v>② 화살비 범위 +[값]%</v>
+        <v>① 관통 사격 위력 +[값]%</v>
       </c>
       <c r="J164" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K24*INDEX(등급!$F$5:$F$12,MATCH($D164,등급!$A$5:$A$12,0)),1)</f>
@@ -33439,7 +32857,7 @@
       </c>
       <c r="I165" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J165" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D165,등급!$A$5:$A$12,0)),1)</f>
@@ -33496,7 +32914,7 @@
       </c>
       <c r="I166" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J166" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D166,등급!$A$5:$A$12,0)),1)</f>
@@ -33553,7 +32971,7 @@
       </c>
       <c r="I167" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J167" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D167,등급!$A$5:$A$12,0)),1)</f>
@@ -33610,7 +33028,7 @@
       </c>
       <c r="I168" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J168" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D168,등급!$A$5:$A$12,0)),1)</f>
@@ -33667,7 +33085,7 @@
       </c>
       <c r="I169" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J169" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D169,등급!$A$5:$A$12,0)),1)</f>
@@ -33724,7 +33142,7 @@
       </c>
       <c r="I170" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J170" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D170,등급!$A$5:$A$12,0)),1)</f>
@@ -33781,7 +33199,7 @@
       </c>
       <c r="I171" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J171" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D171,등급!$A$5:$A$12,0)),1)</f>
@@ -33838,7 +33256,7 @@
       </c>
       <c r="I172" s="19" t="str">
         <f aca="false">장비_기본!J25</f>
-        <v>적이 70px 안에 있으면 받는 피해 -[값]%</v>
+        <v>가까이 붙은 적이 있으면 받는 피해 -[값]%</v>
       </c>
       <c r="J172" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K25*INDEX(등급!$F$5:$F$12,MATCH($D172,등급!$A$5:$A$12,0)),1)</f>
@@ -34343,7 +33761,7 @@
       </c>
       <c r="G181" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H181" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D181,등급!$A$5:$A$12,0))</f>
@@ -34396,7 +33814,7 @@
       </c>
       <c r="G182" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H182" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D182,등급!$A$5:$A$12,0))</f>
@@ -34449,7 +33867,7 @@
       </c>
       <c r="G183" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H183" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D183,등급!$A$5:$A$12,0))</f>
@@ -34502,7 +33920,7 @@
       </c>
       <c r="G184" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H184" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D184,등급!$A$5:$A$12,0))</f>
@@ -34555,7 +33973,7 @@
       </c>
       <c r="G185" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H185" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D185,등급!$A$5:$A$12,0))</f>
@@ -34608,7 +34026,7 @@
       </c>
       <c r="G186" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H186" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D186,등급!$A$5:$A$12,0))</f>
@@ -34661,7 +34079,7 @@
       </c>
       <c r="G187" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H187" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D187,등급!$A$5:$A$12,0))</f>
@@ -34714,7 +34132,7 @@
       </c>
       <c r="G188" s="19" t="str">
         <f aca="false">장비_기본!H27</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H188" s="21" t="n">
         <f aca="false">장비_기본!I27*INDEX(등급!$C$5:$C$12,MATCH($D188,등급!$A$5:$A$12,0))</f>
@@ -34767,7 +34185,7 @@
       </c>
       <c r="G189" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H189" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D189,등급!$A$5:$A$12,0))</f>
@@ -34820,7 +34238,7 @@
       </c>
       <c r="G190" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H190" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D190,등급!$A$5:$A$12,0))</f>
@@ -34873,7 +34291,7 @@
       </c>
       <c r="G191" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H191" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D191,등급!$A$5:$A$12,0))</f>
@@ -34926,7 +34344,7 @@
       </c>
       <c r="G192" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H192" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D192,등급!$A$5:$A$12,0))</f>
@@ -34979,7 +34397,7 @@
       </c>
       <c r="G193" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H193" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D193,등급!$A$5:$A$12,0))</f>
@@ -35032,7 +34450,7 @@
       </c>
       <c r="G194" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H194" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D194,등급!$A$5:$A$12,0))</f>
@@ -35085,7 +34503,7 @@
       </c>
       <c r="G195" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H195" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D195,등급!$A$5:$A$12,0))</f>
@@ -35138,7 +34556,7 @@
       </c>
       <c r="G196" s="19" t="str">
         <f aca="false">장비_기본!H28</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H196" s="21" t="n">
         <f aca="false">장비_기본!I28*INDEX(등급!$C$5:$C$12,MATCH($D196,등급!$A$5:$A$12,0))</f>
@@ -35199,7 +34617,7 @@
       </c>
       <c r="I197" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J197" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D197,등급!$A$5:$A$12,0)),1)</f>
@@ -35256,7 +34674,7 @@
       </c>
       <c r="I198" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J198" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D198,등급!$A$5:$A$12,0)),1)</f>
@@ -35313,7 +34731,7 @@
       </c>
       <c r="I199" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J199" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D199,등급!$A$5:$A$12,0)),1)</f>
@@ -35370,7 +34788,7 @@
       </c>
       <c r="I200" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J200" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D200,등급!$A$5:$A$12,0)),1)</f>
@@ -35427,7 +34845,7 @@
       </c>
       <c r="I201" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J201" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D201,등급!$A$5:$A$12,0)),1)</f>
@@ -35484,7 +34902,7 @@
       </c>
       <c r="I202" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J202" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D202,등급!$A$5:$A$12,0)),1)</f>
@@ -35541,7 +34959,7 @@
       </c>
       <c r="I203" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J203" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D203,등급!$A$5:$A$12,0)),1)</f>
@@ -35598,7 +35016,7 @@
       </c>
       <c r="I204" s="19" t="str">
         <f aca="false">장비_기본!J29</f>
-        <v>① 별빛 탄 화상 피해 +[값]%</v>
+        <v>화상 피해 +[값]%</v>
       </c>
       <c r="J204" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K29*INDEX(등급!$F$5:$F$12,MATCH($D204,등급!$A$5:$A$12,0)),1)</f>
@@ -35655,7 +35073,7 @@
       </c>
       <c r="I205" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J205" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D205,등급!$A$5:$A$12,0)),1)</f>
@@ -35712,7 +35130,7 @@
       </c>
       <c r="I206" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J206" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D206,등급!$A$5:$A$12,0)),1)</f>
@@ -35769,7 +35187,7 @@
       </c>
       <c r="I207" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J207" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D207,등급!$A$5:$A$12,0)),1)</f>
@@ -35826,7 +35244,7 @@
       </c>
       <c r="I208" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J208" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D208,등급!$A$5:$A$12,0)),1)</f>
@@ -35883,7 +35301,7 @@
       </c>
       <c r="I209" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J209" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D209,등급!$A$5:$A$12,0)),1)</f>
@@ -35940,7 +35358,7 @@
       </c>
       <c r="I210" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J210" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D210,등급!$A$5:$A$12,0)),1)</f>
@@ -35997,7 +35415,7 @@
       </c>
       <c r="I211" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J211" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D211,등급!$A$5:$A$12,0)),1)</f>
@@ -36054,7 +35472,7 @@
       </c>
       <c r="I212" s="19" t="str">
         <f aca="false">장비_기본!J30</f>
-        <v>② 유성우 범위 +[값]%</v>
+        <v>② 번개 사슬 위력 +[값]%</v>
       </c>
       <c r="J212" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K30*INDEX(등급!$F$5:$F$12,MATCH($D212,등급!$A$5:$A$12,0)),1)</f>
@@ -36111,7 +35529,7 @@
       </c>
       <c r="I213" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J213" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D213,등급!$A$5:$A$12,0)),1)</f>
@@ -36168,7 +35586,7 @@
       </c>
       <c r="I214" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J214" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D214,등급!$A$5:$A$12,0)),1)</f>
@@ -36225,7 +35643,7 @@
       </c>
       <c r="I215" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J215" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D215,등급!$A$5:$A$12,0)),1)</f>
@@ -36282,7 +35700,7 @@
       </c>
       <c r="I216" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J216" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D216,등급!$A$5:$A$12,0)),1)</f>
@@ -36339,7 +35757,7 @@
       </c>
       <c r="I217" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J217" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D217,등급!$A$5:$A$12,0)),1)</f>
@@ -36396,7 +35814,7 @@
       </c>
       <c r="I218" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J218" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D218,등급!$A$5:$A$12,0)),1)</f>
@@ -36453,7 +35871,7 @@
       </c>
       <c r="I219" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J219" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D219,등급!$A$5:$A$12,0)),1)</f>
@@ -36510,7 +35928,7 @@
       </c>
       <c r="I220" s="19" t="str">
         <f aca="false">장비_기본!J31</f>
-        <v>③ 대마법이 그로기 적에게 위력 +[값]%</v>
+        <v>③ 필살기가 그로기 적에게 주는 피해 +[값]%</v>
       </c>
       <c r="J220" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K31*INDEX(등급!$F$5:$F$12,MATCH($D220,등급!$A$5:$A$12,0)),1)</f>
@@ -37927,7 +37345,7 @@
       </c>
       <c r="G245" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H245" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D245,등급!$A$5:$A$12,0))</f>
@@ -37980,7 +37398,7 @@
       </c>
       <c r="G246" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H246" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D246,등급!$A$5:$A$12,0))</f>
@@ -38033,7 +37451,7 @@
       </c>
       <c r="G247" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H247" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D247,등급!$A$5:$A$12,0))</f>
@@ -38086,7 +37504,7 @@
       </c>
       <c r="G248" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H248" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D248,등급!$A$5:$A$12,0))</f>
@@ -38139,7 +37557,7 @@
       </c>
       <c r="G249" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H249" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D249,등급!$A$5:$A$12,0))</f>
@@ -38192,7 +37610,7 @@
       </c>
       <c r="G250" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H250" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D250,등급!$A$5:$A$12,0))</f>
@@ -38245,7 +37663,7 @@
       </c>
       <c r="G251" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H251" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D251,등급!$A$5:$A$12,0))</f>
@@ -38298,7 +37716,7 @@
       </c>
       <c r="G252" s="19" t="str">
         <f aca="false">장비_기본!H35</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H252" s="21" t="n">
         <f aca="false">장비_기본!I35*INDEX(등급!$C$5:$C$12,MATCH($D252,등급!$A$5:$A$12,0))</f>
@@ -38351,7 +37769,7 @@
       </c>
       <c r="G253" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H253" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D253,등급!$A$5:$A$12,0))</f>
@@ -38404,7 +37822,7 @@
       </c>
       <c r="G254" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H254" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D254,등급!$A$5:$A$12,0))</f>
@@ -38457,7 +37875,7 @@
       </c>
       <c r="G255" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H255" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D255,등급!$A$5:$A$12,0))</f>
@@ -38510,7 +37928,7 @@
       </c>
       <c r="G256" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H256" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D256,등급!$A$5:$A$12,0))</f>
@@ -38563,7 +37981,7 @@
       </c>
       <c r="G257" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H257" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D257,등급!$A$5:$A$12,0))</f>
@@ -38616,7 +38034,7 @@
       </c>
       <c r="G258" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H258" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D258,등급!$A$5:$A$12,0))</f>
@@ -38669,7 +38087,7 @@
       </c>
       <c r="G259" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H259" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D259,등급!$A$5:$A$12,0))</f>
@@ -38722,7 +38140,7 @@
       </c>
       <c r="G260" s="19" t="str">
         <f aca="false">장비_기본!H36</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H260" s="21" t="n">
         <f aca="false">장비_기본!I36*INDEX(등급!$C$5:$C$12,MATCH($D260,등급!$A$5:$A$12,0))</f>
@@ -38783,7 +38201,7 @@
       </c>
       <c r="I261" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J261" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D261,등급!$A$5:$A$12,0)),1)</f>
@@ -38840,7 +38258,7 @@
       </c>
       <c r="I262" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J262" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D262,등급!$A$5:$A$12,0)),1)</f>
@@ -38897,7 +38315,7 @@
       </c>
       <c r="I263" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J263" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D263,등급!$A$5:$A$12,0)),1)</f>
@@ -38954,7 +38372,7 @@
       </c>
       <c r="I264" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J264" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D264,등급!$A$5:$A$12,0)),1)</f>
@@ -39011,7 +38429,7 @@
       </c>
       <c r="I265" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J265" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D265,등급!$A$5:$A$12,0)),1)</f>
@@ -39068,7 +38486,7 @@
       </c>
       <c r="I266" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J266" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D266,등급!$A$5:$A$12,0)),1)</f>
@@ -39125,7 +38543,7 @@
       </c>
       <c r="I267" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J267" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D267,등급!$A$5:$A$12,0)),1)</f>
@@ -39182,7 +38600,7 @@
       </c>
       <c r="I268" s="19" t="str">
         <f aca="false">장비_기본!J37</f>
-        <v>① 치유 회복량 +[값]%</v>
+        <v>② 광역 치유 회복량 +[값]%</v>
       </c>
       <c r="J268" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K37*INDEX(등급!$F$5:$F$12,MATCH($D268,등급!$A$5:$A$12,0)),1)</f>
@@ -39239,7 +38657,7 @@
       </c>
       <c r="I269" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J269" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D269,등급!$A$5:$A$12,0)),1)</f>
@@ -39296,7 +38714,7 @@
       </c>
       <c r="I270" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J270" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D270,등급!$A$5:$A$12,0)),1)</f>
@@ -39353,7 +38771,7 @@
       </c>
       <c r="I271" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J271" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D271,등급!$A$5:$A$12,0)),1)</f>
@@ -39410,7 +38828,7 @@
       </c>
       <c r="I272" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J272" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D272,등급!$A$5:$A$12,0)),1)</f>
@@ -39467,7 +38885,7 @@
       </c>
       <c r="I273" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J273" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D273,등급!$A$5:$A$12,0)),1)</f>
@@ -39524,7 +38942,7 @@
       </c>
       <c r="I274" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J274" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D274,등급!$A$5:$A$12,0)),1)</f>
@@ -39581,7 +38999,7 @@
       </c>
       <c r="I275" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J275" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D275,등급!$A$5:$A$12,0)),1)</f>
@@ -39638,7 +39056,7 @@
       </c>
       <c r="I276" s="19" t="str">
         <f aca="false">장비_기본!J38</f>
-        <v>② 광역 치유 범위 +[값]%</v>
+        <v>② 빛의 심판 위력 +[값]%</v>
       </c>
       <c r="J276" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K38*INDEX(등급!$F$5:$F$12,MATCH($D276,등급!$A$5:$A$12,0)),1)</f>
@@ -39695,7 +39113,7 @@
       </c>
       <c r="I277" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J277" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D277,등급!$A$5:$A$12,0)),1)</f>
@@ -39752,7 +39170,7 @@
       </c>
       <c r="I278" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J278" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D278,등급!$A$5:$A$12,0)),1)</f>
@@ -39809,7 +39227,7 @@
       </c>
       <c r="I279" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J279" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D279,등급!$A$5:$A$12,0)),1)</f>
@@ -39866,7 +39284,7 @@
       </c>
       <c r="I280" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J280" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D280,등급!$A$5:$A$12,0)),1)</f>
@@ -39923,7 +39341,7 @@
       </c>
       <c r="I281" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J281" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D281,등급!$A$5:$A$12,0)),1)</f>
@@ -39980,7 +39398,7 @@
       </c>
       <c r="I282" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J282" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D282,등급!$A$5:$A$12,0)),1)</f>
@@ -40037,7 +39455,7 @@
       </c>
       <c r="I283" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J283" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D283,등급!$A$5:$A$12,0)),1)</f>
@@ -40094,7 +39512,7 @@
       </c>
       <c r="I284" s="19" t="str">
         <f aca="false">장비_기본!J39</f>
-        <v>치유받은 아군 3초간 받는 피해 -[값]%</v>
+        <v>회복받은 아군은 3초간 받는 피해 -[값]%</v>
       </c>
       <c r="J284" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K39*INDEX(등급!$F$5:$F$12,MATCH($D284,등급!$A$5:$A$12,0)),1)</f>
@@ -40151,7 +39569,7 @@
       </c>
       <c r="I285" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J285" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D285,등급!$A$5:$A$12,0)),1)</f>
@@ -40208,7 +39626,7 @@
       </c>
       <c r="I286" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J286" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D286,등급!$A$5:$A$12,0)),1)</f>
@@ -40265,7 +39683,7 @@
       </c>
       <c r="I287" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J287" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D287,등급!$A$5:$A$12,0)),1)</f>
@@ -40322,7 +39740,7 @@
       </c>
       <c r="I288" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J288" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D288,등급!$A$5:$A$12,0)),1)</f>
@@ -40379,7 +39797,7 @@
       </c>
       <c r="I289" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J289" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D289,등급!$A$5:$A$12,0)),1)</f>
@@ -40436,7 +39854,7 @@
       </c>
       <c r="I290" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J290" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D290,등급!$A$5:$A$12,0)),1)</f>
@@ -40493,7 +39911,7 @@
       </c>
       <c r="I291" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J291" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D291,등급!$A$5:$A$12,0)),1)</f>
@@ -40550,7 +39968,7 @@
       </c>
       <c r="I292" s="19" t="str">
         <f aca="false">장비_기본!J40</f>
-        <v>파티 회복 받는 양 +[값]%</v>
+        <v>파티가 받는 회복량 +[값]%</v>
       </c>
       <c r="J292" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K40*INDEX(등급!$F$5:$F$12,MATCH($D292,등급!$A$5:$A$12,0)),1)</f>
@@ -40607,7 +40025,7 @@
       </c>
       <c r="I293" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J293" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D293,등급!$A$5:$A$12,0)),1)</f>
@@ -40664,7 +40082,7 @@
       </c>
       <c r="I294" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J294" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D294,등급!$A$5:$A$12,0)),1)</f>
@@ -40721,7 +40139,7 @@
       </c>
       <c r="I295" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J295" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D295,등급!$A$5:$A$12,0)),1)</f>
@@ -40778,7 +40196,7 @@
       </c>
       <c r="I296" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J296" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D296,등급!$A$5:$A$12,0)),1)</f>
@@ -40835,7 +40253,7 @@
       </c>
       <c r="I297" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J297" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D297,등급!$A$5:$A$12,0)),1)</f>
@@ -40892,7 +40310,7 @@
       </c>
       <c r="I298" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J298" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D298,등급!$A$5:$A$12,0)),1)</f>
@@ -40949,7 +40367,7 @@
       </c>
       <c r="I299" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J299" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D299,등급!$A$5:$A$12,0)),1)</f>
@@ -41006,7 +40424,7 @@
       </c>
       <c r="I300" s="19" t="str">
         <f aca="false">장비_기본!J41</f>
-        <v>③ 생명의 나무 지속 +[값]초</v>
+        <v>① 수호의 기도 공명 지속 +[값]초</v>
       </c>
       <c r="J300" s="20" t="n">
         <f aca="false">ROUND(장비_기본!K41*INDEX(등급!$F$5:$F$12,MATCH($D300,등급!$A$5:$A$12,0)),1)</f>
@@ -41511,7 +40929,7 @@
       </c>
       <c r="G309" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H309" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D309,등급!$A$5:$A$12,0))</f>
@@ -41564,7 +40982,7 @@
       </c>
       <c r="G310" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H310" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D310,등급!$A$5:$A$12,0))</f>
@@ -41617,7 +41035,7 @@
       </c>
       <c r="G311" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H311" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D311,등급!$A$5:$A$12,0))</f>
@@ -41670,7 +41088,7 @@
       </c>
       <c r="G312" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H312" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D312,등급!$A$5:$A$12,0))</f>
@@ -41723,7 +41141,7 @@
       </c>
       <c r="G313" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H313" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D313,등급!$A$5:$A$12,0))</f>
@@ -41776,7 +41194,7 @@
       </c>
       <c r="G314" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H314" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D314,등급!$A$5:$A$12,0))</f>
@@ -41829,7 +41247,7 @@
       </c>
       <c r="G315" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H315" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D315,등급!$A$5:$A$12,0))</f>
@@ -41882,7 +41300,7 @@
       </c>
       <c r="G316" s="19" t="str">
         <f aca="false">장비_기본!H43</f>
-        <v>① 스킬 위력</v>
+        <v>① 갑옷 스킬 위력</v>
       </c>
       <c r="H316" s="21" t="n">
         <f aca="false">장비_기본!I43*INDEX(등급!$C$5:$C$12,MATCH($D316,등급!$A$5:$A$12,0))</f>
@@ -41935,7 +41353,7 @@
       </c>
       <c r="G317" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H317" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D317,등급!$A$5:$A$12,0))</f>
@@ -41988,7 +41406,7 @@
       </c>
       <c r="G318" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H318" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D318,등급!$A$5:$A$12,0))</f>
@@ -42041,7 +41459,7 @@
       </c>
       <c r="G319" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H319" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D319,등급!$A$5:$A$12,0))</f>
@@ -42094,7 +41512,7 @@
       </c>
       <c r="G320" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H320" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D320,등급!$A$5:$A$12,0))</f>
@@ -42147,7 +41565,7 @@
       </c>
       <c r="G321" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H321" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D321,등급!$A$5:$A$12,0))</f>
@@ -42200,7 +41618,7 @@
       </c>
       <c r="G322" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H322" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D322,등급!$A$5:$A$12,0))</f>
@@ -42253,7 +41671,7 @@
       </c>
       <c r="G323" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H323" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D323,등급!$A$5:$A$12,0))</f>
@@ -42306,7 +41724,7 @@
       </c>
       <c r="G324" s="19" t="str">
         <f aca="false">장비_기본!H44</f>
-        <v>② 스킬 위력</v>
+        <v>② 무기 스킬 위력</v>
       </c>
       <c r="H324" s="21" t="n">
         <f aca="false">장비_기본!I44*INDEX(등급!$C$5:$C$12,MATCH($D324,등급!$A$5:$A$12,0))</f>
@@ -47466,7 +46884,7 @@
         <v>359</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>144</v>
+        <v>360</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>4</v>
@@ -47488,10 +46906,10 @@
         <v>139</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>10</v>
@@ -47513,10 +46931,10 @@
         <v>139</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>15</v>
@@ -47541,7 +46959,7 @@
         <v>190</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>10</v>
@@ -47566,7 +46984,7 @@
         <v>211</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>5</v>
@@ -47591,7 +47009,7 @@
         <v>274</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>1</v>
@@ -47615,7 +47033,7 @@
         <v>359</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>15</v>
@@ -47637,10 +47055,10 @@
         <v>172</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>10</v>
@@ -47662,10 +47080,10 @@
         <v>172</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>15</v>
@@ -47690,7 +47108,7 @@
         <v>190</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>189</v>
+        <v>365</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>10</v>
@@ -47715,7 +47133,7 @@
         <v>211</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>15</v>
@@ -47737,10 +47155,10 @@
         <v>172</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>372</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>1</v>
@@ -47749,7 +47167,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">E16/D16</f>
@@ -47764,7 +47182,7 @@
         <v>359</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>15</v>
@@ -47786,10 +47204,10 @@
         <v>201</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>10</v>
@@ -47811,10 +47229,10 @@
         <v>201</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>15</v>
@@ -47839,7 +47257,7 @@
         <v>190</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>10</v>
@@ -47864,7 +47282,7 @@
         <v>211</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>15</v>
@@ -47886,10 +47304,10 @@
         <v>201</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>12</v>
@@ -47914,7 +47332,7 @@
         <v>359</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>15</v>
@@ -47936,10 +47354,10 @@
         <v>229</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>10</v>
@@ -47961,10 +47379,10 @@
         <v>229</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>15</v>
@@ -47989,7 +47407,7 @@
         <v>190</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>10</v>
@@ -48014,7 +47432,7 @@
         <v>211</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>15</v>
@@ -48036,10 +47454,10 @@
         <v>229</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>12</v>
@@ -48064,7 +47482,7 @@
         <v>359</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>258</v>
+        <v>375</v>
       </c>
       <c r="D29" s="10" t="n">
         <v>15</v>
@@ -48086,10 +47504,10 @@
         <v>257</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>10</v>
@@ -48111,10 +47529,10 @@
         <v>257</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>15</v>
@@ -48139,7 +47557,7 @@
         <v>190</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>10</v>
@@ -48164,7 +47582,7 @@
         <v>211</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>15</v>
@@ -48189,7 +47607,7 @@
         <v>274</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>1</v>
@@ -48213,7 +47631,7 @@
         <v>359</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>10</v>
@@ -48235,10 +47653,10 @@
         <v>286</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>10</v>
@@ -48263,7 +47681,7 @@
         <v>211</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>10</v>
@@ -48285,10 +47703,10 @@
         <v>286</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>7</v>
@@ -48313,7 +47731,7 @@
         <v>190</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>7</v>
@@ -48335,10 +47753,10 @@
         <v>286</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>8</v>
@@ -48381,7 +47799,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -48397,7 +47815,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -48413,7 +47831,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="B3" s="26" t="n">
         <v>0.6</v>
@@ -48434,13 +47852,13 @@
         <v>68</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>43</v>
@@ -48469,10 +47887,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>84</v>
@@ -48515,10 +47933,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>87</v>
@@ -48561,10 +47979,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>99</v>
@@ -48607,10 +48025,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>93</v>
@@ -48653,10 +48071,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>97</v>
@@ -48699,10 +48117,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>89</v>
@@ -48745,10 +48163,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>103</v>
@@ -48791,10 +48209,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>101</v>
@@ -48837,10 +48255,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>112</v>
@@ -48897,7 +48315,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -48920,7 +48338,7 @@
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="29" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="E16" s="30" t="s">
         <v>43</v>
@@ -48952,7 +48370,7 @@
         <v>359</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>419</v>
+        <v>115</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="18" t="n">
@@ -48993,10 +48411,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>420</v>
+        <v>118</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="18" t="n">
@@ -49040,7 +48458,7 @@
         <v>211</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="18" t="n">
@@ -49095,7 +48513,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
